--- a/Result/profitability/5523.xlsx
+++ b/Result/profitability/5523.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.008749999999999945</v>
+        <v>-0.01249999999999995</v>
       </c>
       <c r="N2" t="n">
-        <v>68.11624999999999</v>
+        <v>69.05249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02625000000000006</v>
+        <v>0.02000000000000006</v>
       </c>
       <c r="N3" t="n">
-        <v>64.7625</v>
+        <v>72.05125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00125000000000006</v>
+        <v>6.245004513516506e-17</v>
       </c>
       <c r="N4" t="n">
-        <v>64.29625</v>
+        <v>64.28375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05374999999999994</v>
+        <v>-0.05499999999999994</v>
       </c>
       <c r="N5" t="n">
-        <v>51.02250000000001</v>
+        <v>51.0375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>-0.06624999999999995</v>
       </c>
       <c r="N6" t="n">
-        <v>42.63125</v>
+        <v>46.9975</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06749999999999995</v>
+        <v>-0.06999999999999995</v>
       </c>
       <c r="N7" t="n">
-        <v>37.35375</v>
+        <v>37.37375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08249999999999995</v>
+        <v>-0.08124999999999995</v>
       </c>
       <c r="N8" t="n">
-        <v>33.38375</v>
+        <v>33.36625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5523</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-575.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.01624999999999995</v>
+      </c>
+      <c r="N75" t="n">
+        <v>75.56375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1400000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.001585503963759893</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.009999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1199999999999903</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.001363016810540518</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
